--- a/cds_files/IowaState_CDS_2025-2026.xlsx
+++ b/cds_files/IowaState_CDS_2025-2026.xlsx
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
   </sheetData>
